--- a/85_Web_Application_Test_Cases/85_Web_Application_Test_Cases.xlsx
+++ b/85_Web_Application_Test_Cases/85_Web_Application_Test_Cases.xlsx
@@ -439,9 +439,6 @@
     <t>Verify Alena Burtysh bio card details and text</t>
   </si>
   <si>
-    <t>Verify Dmytro Kravchenko bio card details and text</t>
-  </si>
-  <si>
     <t>Verify Inna Shevchenko bio card details and text</t>
   </si>
   <si>
@@ -1076,6 +1073,9 @@
   </si>
   <si>
     <t>Hover with mouse over the picture asset of Dmitry Kravchenko.</t>
+  </si>
+  <si>
+    <t>Verify Dmitry Kravchenko bio card details and text</t>
   </si>
 </sst>
 </file>
@@ -1546,16 +1546,16 @@
         <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1566,16 +1566,16 @@
         <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1586,16 +1586,16 @@
         <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1606,16 +1606,16 @@
         <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F5" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1626,16 +1626,16 @@
         <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1646,16 +1646,16 @@
         <v>96</v>
       </c>
       <c r="C7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1666,16 +1666,16 @@
         <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1686,16 +1686,16 @@
         <v>98</v>
       </c>
       <c r="C9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F9" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1706,16 +1706,16 @@
         <v>99</v>
       </c>
       <c r="C10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E10" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1726,16 +1726,16 @@
         <v>100</v>
       </c>
       <c r="C11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E11" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F11" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1746,16 +1746,16 @@
         <v>101</v>
       </c>
       <c r="C12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1766,16 +1766,16 @@
         <v>102</v>
       </c>
       <c r="C13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F13" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1786,16 +1786,16 @@
         <v>103</v>
       </c>
       <c r="C14" t="s">
+        <v>344</v>
+      </c>
+      <c r="D14" t="s">
+        <v>191</v>
+      </c>
+      <c r="E14" t="s">
         <v>345</v>
       </c>
-      <c r="D14" t="s">
-        <v>192</v>
-      </c>
-      <c r="E14" t="s">
-        <v>346</v>
-      </c>
       <c r="F14" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1803,19 +1803,19 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
+        <v>347</v>
+      </c>
+      <c r="C15" t="s">
+        <v>344</v>
+      </c>
+      <c r="D15" t="s">
+        <v>349</v>
+      </c>
+      <c r="E15" t="s">
         <v>348</v>
       </c>
-      <c r="C15" t="s">
-        <v>345</v>
-      </c>
-      <c r="D15" t="s">
-        <v>350</v>
-      </c>
-      <c r="E15" t="s">
-        <v>349</v>
-      </c>
       <c r="F15" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1826,16 +1826,16 @@
         <v>104</v>
       </c>
       <c r="C16" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F16" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1846,16 +1846,16 @@
         <v>105</v>
       </c>
       <c r="C17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E17" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1866,16 +1866,16 @@
         <v>106</v>
       </c>
       <c r="C18" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E18" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F18" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1886,16 +1886,16 @@
         <v>107</v>
       </c>
       <c r="C19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D19" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E19" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F19" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1906,16 +1906,16 @@
         <v>108</v>
       </c>
       <c r="C20" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E20" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F20" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1926,16 +1926,16 @@
         <v>109</v>
       </c>
       <c r="C21" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D21" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E21" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F21" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1946,16 +1946,16 @@
         <v>110</v>
       </c>
       <c r="C22" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D22" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E22" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F22" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1966,16 +1966,16 @@
         <v>111</v>
       </c>
       <c r="C23" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D23" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E23" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F23" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1986,16 +1986,16 @@
         <v>112</v>
       </c>
       <c r="C24" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D24" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F24" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2006,16 +2006,16 @@
         <v>113</v>
       </c>
       <c r="C25" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D25" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E25" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F25" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2026,16 +2026,16 @@
         <v>114</v>
       </c>
       <c r="C26" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E26" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F26" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2046,16 +2046,16 @@
         <v>115</v>
       </c>
       <c r="C27" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D27" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E27" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F27" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2066,16 +2066,16 @@
         <v>116</v>
       </c>
       <c r="C28" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D28" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E28" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F28" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2086,16 +2086,16 @@
         <v>117</v>
       </c>
       <c r="C29" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D29" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E29" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F29" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2106,16 +2106,16 @@
         <v>118</v>
       </c>
       <c r="C30" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F30" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2126,16 +2126,16 @@
         <v>119</v>
       </c>
       <c r="C31" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D31" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E31" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F31" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2146,16 +2146,16 @@
         <v>120</v>
       </c>
       <c r="C32" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D32" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E32" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F32" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2166,16 +2166,16 @@
         <v>121</v>
       </c>
       <c r="C33" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D33" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E33" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F33" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2186,16 +2186,16 @@
         <v>122</v>
       </c>
       <c r="C34" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D34" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E34" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F34" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2206,16 +2206,16 @@
         <v>123</v>
       </c>
       <c r="C35" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D35" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E35" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F35" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2226,16 +2226,16 @@
         <v>124</v>
       </c>
       <c r="C36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D36" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E36" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F36" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2246,16 +2246,16 @@
         <v>125</v>
       </c>
       <c r="C37" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D37" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E37" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F37" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2266,16 +2266,16 @@
         <v>126</v>
       </c>
       <c r="C38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E38" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F38" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2286,16 +2286,16 @@
         <v>127</v>
       </c>
       <c r="C39" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D39" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E39" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F39" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2306,16 +2306,16 @@
         <v>128</v>
       </c>
       <c r="C40" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D40" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E40" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F40" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2326,16 +2326,16 @@
         <v>129</v>
       </c>
       <c r="C41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D41" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E41" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F41" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2346,16 +2346,16 @@
         <v>130</v>
       </c>
       <c r="C42" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D42" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E42" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F42" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2366,16 +2366,16 @@
         <v>131</v>
       </c>
       <c r="C43" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D43" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E43" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F43" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2386,16 +2386,16 @@
         <v>132</v>
       </c>
       <c r="C44" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D44" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E44" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F44" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2406,16 +2406,16 @@
         <v>133</v>
       </c>
       <c r="C45" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D45" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E45" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F45" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2426,16 +2426,16 @@
         <v>134</v>
       </c>
       <c r="C46" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D46" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E46" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F46" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2446,16 +2446,16 @@
         <v>135</v>
       </c>
       <c r="C47" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D47" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E47" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F47" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2466,16 +2466,16 @@
         <v>136</v>
       </c>
       <c r="C48" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D48" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E48" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F48" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2486,16 +2486,16 @@
         <v>137</v>
       </c>
       <c r="C49" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D49" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E49" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F49" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2506,16 +2506,16 @@
         <v>138</v>
       </c>
       <c r="C50" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D50" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E50" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F50" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2526,16 +2526,16 @@
         <v>139</v>
       </c>
       <c r="C51" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D51" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E51" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F51" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2546,16 +2546,16 @@
         <v>140</v>
       </c>
       <c r="C52" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D52" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E52" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F52" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2563,19 +2563,19 @@
         <v>57</v>
       </c>
       <c r="B53" t="s">
-        <v>141</v>
+        <v>353</v>
       </c>
       <c r="C53" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D53" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E53" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F53" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2583,19 +2583,19 @@
         <v>58</v>
       </c>
       <c r="B54" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C54" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D54" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E54" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F54" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2603,19 +2603,19 @@
         <v>59</v>
       </c>
       <c r="B55" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C55" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D55" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E55" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F55" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2623,19 +2623,19 @@
         <v>60</v>
       </c>
       <c r="B56" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C56" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D56" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E56" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F56" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2643,19 +2643,19 @@
         <v>61</v>
       </c>
       <c r="B57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C57" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D57" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E57" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F57" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2663,19 +2663,19 @@
         <v>62</v>
       </c>
       <c r="B58" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C58" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E58" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F58" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2683,19 +2683,19 @@
         <v>63</v>
       </c>
       <c r="B59" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C59" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D59" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E59" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F59" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2703,19 +2703,19 @@
         <v>64</v>
       </c>
       <c r="B60" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C60" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D60" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E60" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F60" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2723,19 +2723,19 @@
         <v>65</v>
       </c>
       <c r="B61" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C61" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D61" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E61" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F61" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2743,19 +2743,19 @@
         <v>66</v>
       </c>
       <c r="B62" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C62" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D62" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E62" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F62" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2763,19 +2763,19 @@
         <v>67</v>
       </c>
       <c r="B63" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D63" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E63" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F63" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2783,19 +2783,19 @@
         <v>68</v>
       </c>
       <c r="B64" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C64" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D64" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E64" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F64" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2803,19 +2803,19 @@
         <v>69</v>
       </c>
       <c r="B65" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C65" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D65" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E65" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F65" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2823,19 +2823,19 @@
         <v>70</v>
       </c>
       <c r="B66" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C66" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D66" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E66" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F66" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2843,19 +2843,19 @@
         <v>71</v>
       </c>
       <c r="B67" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C67" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D67" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E67" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F67" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2863,19 +2863,19 @@
         <v>72</v>
       </c>
       <c r="B68" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D68" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E68" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F68" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2883,19 +2883,19 @@
         <v>73</v>
       </c>
       <c r="B69" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C69" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D69" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E69" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F69" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -2903,19 +2903,19 @@
         <v>74</v>
       </c>
       <c r="B70" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C70" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D70" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E70" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F70" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2923,19 +2923,19 @@
         <v>75</v>
       </c>
       <c r="B71" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C71" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D71" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E71" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F71" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2943,19 +2943,19 @@
         <v>76</v>
       </c>
       <c r="B72" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C72" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D72" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E72" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F72" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2963,19 +2963,19 @@
         <v>77</v>
       </c>
       <c r="B73" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C73" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D73" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E73" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F73" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2983,19 +2983,19 @@
         <v>78</v>
       </c>
       <c r="B74" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C74" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D74" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E74" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F74" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3003,19 +3003,19 @@
         <v>79</v>
       </c>
       <c r="B75" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C75" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D75" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E75" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F75" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3023,19 +3023,19 @@
         <v>80</v>
       </c>
       <c r="B76" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C76" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D76" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E76" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F76" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3043,19 +3043,19 @@
         <v>81</v>
       </c>
       <c r="B77" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C77" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D77" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E77" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F77" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3063,19 +3063,19 @@
         <v>82</v>
       </c>
       <c r="B78" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C78" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D78" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E78" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F78" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3083,19 +3083,19 @@
         <v>83</v>
       </c>
       <c r="B79" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C79" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D79" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E79" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F79" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3103,19 +3103,19 @@
         <v>84</v>
       </c>
       <c r="B80" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C80" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D80" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E80" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F80" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3123,19 +3123,19 @@
         <v>85</v>
       </c>
       <c r="B81" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C81" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D81" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E81" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F81" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3143,19 +3143,19 @@
         <v>86</v>
       </c>
       <c r="B82" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C82" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D82" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E82" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F82" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3163,19 +3163,19 @@
         <v>87</v>
       </c>
       <c r="B83" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C83" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D83" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E83" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F83" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3183,19 +3183,19 @@
         <v>88</v>
       </c>
       <c r="B84" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C84" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D84" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E84" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F84" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3203,19 +3203,19 @@
         <v>89</v>
       </c>
       <c r="B85" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C85" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D85" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E85" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F85" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3223,19 +3223,19 @@
         <v>90</v>
       </c>
       <c r="B86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C86" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D86" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E86" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F86" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>

--- a/85_Web_Application_Test_Cases/85_Web_Application_Test_Cases.xlsx
+++ b/85_Web_Application_Test_Cases/85_Web_Application_Test_Cases.xlsx
@@ -943,9 +943,6 @@
     <t>Locate the card profile widget for instructor Alena Burtysh.</t>
   </si>
   <si>
-    <t>Locate the card profile widget for instructor Dmytro Kravchenko.</t>
-  </si>
-  <si>
     <t>Locate the card profile widget for instructor Inna Shevchenko.</t>
   </si>
   <si>
@@ -1076,6 +1073,9 @@
   </si>
   <si>
     <t>Verify Dmitry Kravchenko bio card details and text</t>
+  </si>
+  <si>
+    <t>Locate the card profile widget for instructor Dmitry Kravchenko.</t>
   </si>
 </sst>
 </file>
@@ -1555,7 +1555,7 @@
         <v>263</v>
       </c>
       <c r="F2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1575,7 +1575,7 @@
         <v>264</v>
       </c>
       <c r="F3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1595,7 +1595,7 @@
         <v>265</v>
       </c>
       <c r="F4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1615,7 +1615,7 @@
         <v>266</v>
       </c>
       <c r="F5" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1635,7 +1635,7 @@
         <v>267</v>
       </c>
       <c r="F6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1655,7 +1655,7 @@
         <v>268</v>
       </c>
       <c r="F7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1675,7 +1675,7 @@
         <v>269</v>
       </c>
       <c r="F8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1695,7 +1695,7 @@
         <v>270</v>
       </c>
       <c r="F9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1715,7 +1715,7 @@
         <v>271</v>
       </c>
       <c r="F10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1732,10 +1732,10 @@
         <v>188</v>
       </c>
       <c r="E11" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F11" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1755,7 +1755,7 @@
         <v>272</v>
       </c>
       <c r="F12" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1775,7 +1775,7 @@
         <v>273</v>
       </c>
       <c r="F13" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1786,16 +1786,16 @@
         <v>103</v>
       </c>
       <c r="C14" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D14" t="s">
         <v>191</v>
       </c>
       <c r="E14" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F14" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1803,19 +1803,19 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
+        <v>346</v>
+      </c>
+      <c r="C15" t="s">
+        <v>343</v>
+      </c>
+      <c r="D15" t="s">
+        <v>348</v>
+      </c>
+      <c r="E15" t="s">
         <v>347</v>
       </c>
-      <c r="C15" t="s">
-        <v>344</v>
-      </c>
-      <c r="D15" t="s">
-        <v>349</v>
-      </c>
-      <c r="E15" t="s">
-        <v>348</v>
-      </c>
       <c r="F15" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1826,16 +1826,16 @@
         <v>104</v>
       </c>
       <c r="C16" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D16" t="s">
         <v>192</v>
       </c>
       <c r="E16" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F16" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1855,7 +1855,7 @@
         <v>274</v>
       </c>
       <c r="F17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1875,7 +1875,7 @@
         <v>275</v>
       </c>
       <c r="F18" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1895,7 +1895,7 @@
         <v>276</v>
       </c>
       <c r="F19" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1915,7 +1915,7 @@
         <v>277</v>
       </c>
       <c r="F20" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1935,7 +1935,7 @@
         <v>278</v>
       </c>
       <c r="F21" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1955,7 +1955,7 @@
         <v>279</v>
       </c>
       <c r="F22" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1975,7 +1975,7 @@
         <v>280</v>
       </c>
       <c r="F23" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1995,7 +1995,7 @@
         <v>281</v>
       </c>
       <c r="F24" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2015,7 +2015,7 @@
         <v>282</v>
       </c>
       <c r="F25" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2035,7 +2035,7 @@
         <v>283</v>
       </c>
       <c r="F26" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2055,7 +2055,7 @@
         <v>284</v>
       </c>
       <c r="F27" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2075,7 +2075,7 @@
         <v>285</v>
       </c>
       <c r="F28" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2095,7 +2095,7 @@
         <v>286</v>
       </c>
       <c r="F29" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2115,7 +2115,7 @@
         <v>287</v>
       </c>
       <c r="F30" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2135,7 +2135,7 @@
         <v>288</v>
       </c>
       <c r="F31" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2155,7 +2155,7 @@
         <v>289</v>
       </c>
       <c r="F32" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2175,7 +2175,7 @@
         <v>290</v>
       </c>
       <c r="F33" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2195,7 +2195,7 @@
         <v>291</v>
       </c>
       <c r="F34" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2215,7 +2215,7 @@
         <v>292</v>
       </c>
       <c r="F35" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2235,7 +2235,7 @@
         <v>293</v>
       </c>
       <c r="F36" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2255,7 +2255,7 @@
         <v>294</v>
       </c>
       <c r="F37" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2275,7 +2275,7 @@
         <v>295</v>
       </c>
       <c r="F38" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2295,7 +2295,7 @@
         <v>296</v>
       </c>
       <c r="F39" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2315,7 +2315,7 @@
         <v>297</v>
       </c>
       <c r="F40" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2335,7 +2335,7 @@
         <v>298</v>
       </c>
       <c r="F41" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2355,7 +2355,7 @@
         <v>299</v>
       </c>
       <c r="F42" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2375,7 +2375,7 @@
         <v>300</v>
       </c>
       <c r="F43" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2395,7 +2395,7 @@
         <v>301</v>
       </c>
       <c r="F44" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2415,7 +2415,7 @@
         <v>302</v>
       </c>
       <c r="F45" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2435,7 +2435,7 @@
         <v>303</v>
       </c>
       <c r="F46" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2455,7 +2455,7 @@
         <v>304</v>
       </c>
       <c r="F47" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2475,7 +2475,7 @@
         <v>305</v>
       </c>
       <c r="F48" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2495,7 +2495,7 @@
         <v>306</v>
       </c>
       <c r="F49" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2512,10 +2512,10 @@
         <v>226</v>
       </c>
       <c r="E50" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F50" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2535,7 +2535,7 @@
         <v>307</v>
       </c>
       <c r="F51" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2555,7 +2555,7 @@
         <v>308</v>
       </c>
       <c r="F52" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2563,7 +2563,7 @@
         <v>57</v>
       </c>
       <c r="B53" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C53" t="s">
         <v>177</v>
@@ -2572,10 +2572,10 @@
         <v>229</v>
       </c>
       <c r="E53" t="s">
-        <v>309</v>
+        <v>353</v>
       </c>
       <c r="F53" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2592,10 +2592,10 @@
         <v>230</v>
       </c>
       <c r="E54" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F54" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2612,10 +2612,10 @@
         <v>231</v>
       </c>
       <c r="E55" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F55" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2632,10 +2632,10 @@
         <v>232</v>
       </c>
       <c r="E56" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F56" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2652,10 +2652,10 @@
         <v>233</v>
       </c>
       <c r="E57" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F57" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2672,10 +2672,10 @@
         <v>234</v>
       </c>
       <c r="E58" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F58" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2692,10 +2692,10 @@
         <v>235</v>
       </c>
       <c r="E59" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F59" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2712,10 +2712,10 @@
         <v>236</v>
       </c>
       <c r="E60" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F60" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2732,10 +2732,10 @@
         <v>237</v>
       </c>
       <c r="E61" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F61" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2752,10 +2752,10 @@
         <v>238</v>
       </c>
       <c r="E62" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F62" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2772,10 +2772,10 @@
         <v>239</v>
       </c>
       <c r="E63" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F63" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2792,10 +2792,10 @@
         <v>240</v>
       </c>
       <c r="E64" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F64" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2812,10 +2812,10 @@
         <v>241</v>
       </c>
       <c r="E65" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F65" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2832,10 +2832,10 @@
         <v>242</v>
       </c>
       <c r="E66" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F66" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2852,10 +2852,10 @@
         <v>243</v>
       </c>
       <c r="E67" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F67" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2872,10 +2872,10 @@
         <v>244</v>
       </c>
       <c r="E68" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F68" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2892,10 +2892,10 @@
         <v>245</v>
       </c>
       <c r="E69" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F69" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -2912,10 +2912,10 @@
         <v>246</v>
       </c>
       <c r="E70" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F70" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2932,10 +2932,10 @@
         <v>247</v>
       </c>
       <c r="E71" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F71" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2952,10 +2952,10 @@
         <v>248</v>
       </c>
       <c r="E72" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F72" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2972,10 +2972,10 @@
         <v>249</v>
       </c>
       <c r="E73" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F73" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2992,10 +2992,10 @@
         <v>250</v>
       </c>
       <c r="E74" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F74" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3012,10 +3012,10 @@
         <v>251</v>
       </c>
       <c r="E75" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F75" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3032,10 +3032,10 @@
         <v>252</v>
       </c>
       <c r="E76" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F76" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3052,10 +3052,10 @@
         <v>253</v>
       </c>
       <c r="E77" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F77" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3072,10 +3072,10 @@
         <v>254</v>
       </c>
       <c r="E78" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F78" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3092,10 +3092,10 @@
         <v>255</v>
       </c>
       <c r="E79" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F79" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3112,10 +3112,10 @@
         <v>256</v>
       </c>
       <c r="E80" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F80" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3132,10 +3132,10 @@
         <v>257</v>
       </c>
       <c r="E81" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F81" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3152,10 +3152,10 @@
         <v>258</v>
       </c>
       <c r="E82" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F82" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3172,10 +3172,10 @@
         <v>259</v>
       </c>
       <c r="E83" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F83" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3192,10 +3192,10 @@
         <v>260</v>
       </c>
       <c r="E84" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F84" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3212,10 +3212,10 @@
         <v>261</v>
       </c>
       <c r="E85" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F85" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3232,10 +3232,10 @@
         <v>262</v>
       </c>
       <c r="E86" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F86" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
   </sheetData>

--- a/85_Web_Application_Test_Cases/85_Web_Application_Test_Cases.xlsx
+++ b/85_Web_Application_Test_Cases/85_Web_Application_Test_Cases.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="358">
   <si>
     <t>ID</t>
   </si>
@@ -325,9 +325,6 @@
     <t>Verify FAQ section accordion expand/collapse behavior</t>
   </si>
   <si>
-    <t>Verify page loading speed metrics for corporate overview</t>
-  </si>
-  <si>
     <t>Verify copyright year updates dynamically to current year</t>
   </si>
   <si>
@@ -439,6 +436,9 @@
     <t>Verify Alena Burtysh bio card details and text</t>
   </si>
   <si>
+    <t>Verify Dmitry Kravchenko bio card details and text</t>
+  </si>
+  <si>
     <t>Verify Inna Shevchenko bio card details and text</t>
   </si>
   <si>
@@ -469,9 +469,6 @@
     <t>Verify team section sub-headline text value correctness</t>
   </si>
   <si>
-    <t>Verify page responsiveness for mobile flexbox team list</t>
-  </si>
-  <si>
     <t>Verify hover state transparency overlay on teacher portraits</t>
   </si>
   <si>
@@ -520,39 +517,48 @@
     <t>Verify brand font typography recommendation family listing</t>
   </si>
   <si>
-    <t>Verify image file size badge layout under thumbnail items</t>
-  </si>
-  <si>
-    <t>Verify copy color token action button to clipboard link</t>
-  </si>
-  <si>
-    <t>Verify aspect ratio constraint summary instructions presence</t>
-  </si>
-  <si>
-    <t>Verify padding safety zone illustration rendering clarity</t>
-  </si>
-  <si>
-    <t>Verify press contact link under media kit assets footer</t>
-  </si>
-  <si>
-    <t>Verify vector asset pack .SVG file option availability text</t>
+    <t>Verify successful user registration with valid data</t>
+  </si>
+  <si>
+    <t>Verify validation error for empty mandatory fields</t>
+  </si>
+  <si>
+    <t>Verify registration fails with invalid email format</t>
+  </si>
+  <si>
+    <t>Verify user record creation in the database (SQL)</t>
+  </si>
+  <si>
+    <t>Verify DB UNIQUE constraint prevents duplicate emails (SQL)</t>
   </si>
   <si>
     <t>User is on the 'About Us' page.</t>
   </si>
   <si>
+    <t>User is on the 'Theory' page.</t>
+  </si>
+  <si>
     <t>User is on the 'Courses' catalog page.</t>
   </si>
   <si>
     <t>User is on the 'Bugs &amp; Test Cases' page.</t>
   </si>
   <si>
-    <t>User is on the 'Team / Instructors' page.</t>
-  </si>
-  <si>
     <t>User is on the 'Brand Identity' media page.</t>
   </si>
   <si>
+    <t>User is on the Registration page.</t>
+  </si>
+  <si>
+    <t>User 'test_user@mail.com' just registered successfully. DB access is granted.</t>
+  </si>
+  <si>
+    <t>User registered successfully. DB access is granted.</t>
+  </si>
+  <si>
+    <t>User with 'test_user@mail.com' already exists in the database.</t>
+  </si>
+  <si>
     <t>Main heading is clearly visible at the top.</t>
   </si>
   <si>
@@ -592,6 +598,9 @@
     <t>Page fully loads in less than 2 seconds.</t>
   </si>
   <si>
+    <t>Theory handbook PDF starts downloading.</t>
+  </si>
+  <si>
     <t>Footer shows correct current copyright year.</t>
   </si>
   <si>
@@ -736,9 +745,6 @@
     <t>Subheader correctly reads 'Mentorship from Industry Leaders'.</t>
   </si>
   <si>
-    <t>Team card layout wraps cleanly into a single item list sequence.</t>
-  </si>
-  <si>
     <t>Portrait darkens slightly showing social media follow link options.</t>
   </si>
   <si>
@@ -787,22 +793,22 @@
     <t>Primary font family 'Inter' or 'Roboto' is specified in guide text.</t>
   </si>
   <si>
-    <t>File size indicators like 'PNG - 240KB' are present and clear.</t>
-  </si>
-  <si>
-    <t>Notification toast confirms hex color value copied successfully.</t>
-  </si>
-  <si>
-    <t>Text note specifies maintaining original proportions without stretching.</t>
-  </si>
-  <si>
-    <t>Graphic diagram demonstrating clear space borders shows up safely.</t>
-  </si>
-  <si>
-    <t>Navigation brings focus directly onto the PR inquiry input form block.</t>
-  </si>
-  <si>
-    <t>Text notes state scalable format is included in bundle archives.</t>
+    <t>User is redirected to Dashboard. Success message 'Registration successful' is displayed.</t>
+  </si>
+  <si>
+    <t>Red validation errors 'This field is required' appear under First Name, Email, and Password fields.</t>
+  </si>
+  <si>
+    <t>Registration is blocked. Error 'Please enter a valid email address' is displayed.</t>
+  </si>
+  <si>
+    <t>Query returns 1 row. Columns 'first_name', 'last_name', and 'email' match the data entered in UI.</t>
+  </si>
+  <si>
+    <t>The 'password_hash' column contains a securely hashed string (e.g., bcrypt format), not plain text.</t>
+  </si>
+  <si>
+    <t>UI displays 'Email already exists'. SQL query returns exactly 1 (duplicate row was not created).</t>
   </si>
   <si>
     <t>Navigate to the 'About Us' page and check the header element.</t>
@@ -832,12 +838,24 @@
     <t>Click on 'Contact Corporate' text link.</t>
   </si>
   <si>
+    <t>Click language dropdown and change from Ukrainian to English.</t>
+  </si>
+  <si>
     <t>Scroll to footer and click on 'Legal Disclaimer' link.</t>
   </si>
   <si>
     <t>Click on the first question inside the FAQ section.</t>
   </si>
   <si>
+    <t>Reload the 'Theory' page with network tab active.</t>
+  </si>
+  <si>
+    <t>Click on the 'Download Theory Handbook' button.</t>
+  </si>
+  <si>
+    <t>Scroll to the bottom footer of the Theory page...</t>
+  </si>
+  <si>
     <t>Open the 'Courses' tab and check the main page title.</t>
   </si>
   <si>
@@ -937,12 +955,18 @@
     <t>Scroll to the detailed view section of any logged bug item.</t>
   </si>
   <si>
+    <t>Inspect a logged bug card containing a dummy screenshot attachment.</t>
+  </si>
+  <si>
     <t>Navigate to the team overview section page layout header.</t>
   </si>
   <si>
     <t>Locate the card profile widget for instructor Alena Burtysh.</t>
   </si>
   <si>
+    <t>Locate the card profile widget for instructor Dmitry Kravchenko.</t>
+  </si>
+  <si>
     <t>Locate the card profile widget for instructor Inna Shevchenko.</t>
   </si>
   <si>
@@ -973,7 +997,7 @@
     <t>Inspect text node underneath the main mentor page header module.</t>
   </si>
   <si>
-    <t>Switch viewport preview setting to mobile phone resolution profile.</t>
+    <t>Hover with mouse over the picture asset of Dmitry Kravchenko.</t>
   </si>
   <si>
     <t>Check the count badge text next to the section title header group.</t>
@@ -1021,61 +1045,49 @@
     <t>Locate the typography guidelines row inside asset spec matrix.</t>
   </si>
   <si>
-    <t>Inspect text metrics labels below the logo asset display window.</t>
-  </si>
-  <si>
-    <t>Click on the color copy action shortcut token for primary brand color.</t>
-  </si>
-  <si>
-    <t>Review the safety spacing padding guidelines paragraph documentation.</t>
-  </si>
-  <si>
-    <t>Inspect the visual mockup sample showing safety border lines.</t>
-  </si>
-  <si>
-    <t>Click the 'Press Relations Contact' shortcut hyperlink element.</t>
-  </si>
-  <si>
-    <t>Verify text inside the file format compatibility matrix legend block.</t>
-  </si>
-  <si>
     <t>Passed</t>
   </si>
   <si>
     <t>Failed</t>
   </si>
   <si>
-    <t>User is on the 'Theory' page.</t>
-  </si>
-  <si>
-    <t>Reload the 'Theory' page with network tab active.</t>
-  </si>
-  <si>
-    <t>Scroll to the bottom footer of the Theory page...</t>
-  </si>
-  <si>
-    <t>Verify document download link for learning handbook.</t>
-  </si>
-  <si>
-    <t>Click on the 'Download Theory Handbook' button.</t>
-  </si>
-  <si>
-    <t>Theory handbook PDF starts downloading.</t>
-  </si>
-  <si>
-    <t>Inspect a logged bug card containing a dummy screenshot attachment.</t>
-  </si>
-  <si>
-    <t>Click language dropdown and change from Ukrainian to English.</t>
-  </si>
-  <si>
-    <t>Hover with mouse over the picture asset of Dmitry Kravchenko.</t>
-  </si>
-  <si>
-    <t>Verify Dmitry Kravchenko bio card details and text</t>
-  </si>
-  <si>
-    <t>Locate the card profile widget for instructor Dmitry Kravchenko.</t>
+    <t>Verify password is hashed in the database (SQL)</t>
+  </si>
+  <si>
+    <t>User is on the 'About Us' page (Team / Instructors section).</t>
+  </si>
+  <si>
+    <t>Resize browser window to minimum supported desktop width (1280px) and inspect mentor card flexbox layout.</t>
+  </si>
+  <si>
+    <t>Verify mentor card grid alignment at minimum desktop resolution (1280px)</t>
+  </si>
+  <si>
+    <t>Mentor cards maintain proper multi-column grid alignment with preserved margins, padding, and no overlapping elements.</t>
+  </si>
+  <si>
+    <t>Verify page loading speed metrics for handbook &amp; theory page</t>
+  </si>
+  <si>
+    <t>Verify document download link for learning handbook</t>
+  </si>
+  <si>
+    <t>Connect to DB and execute: SELECT * FROM users WHERE email = 'test_user@mail.com'.</t>
+  </si>
+  <si>
+    <t>Connect to DB and execute: SELECT password_hash FROM users WHERE email = 'test_user@mail.com'.</t>
+  </si>
+  <si>
+    <t>Try to register a new account with 'test_user@mail.com' and execute: SELECT COUNT(*) FROM users WHERE email = 'test_user@mail.com'.</t>
+  </si>
+  <si>
+    <t>Fill all mandatory fields with valid data and click 'Register' button.</t>
+  </si>
+  <si>
+    <t>Leave all input fields empty and click 'Register' button.</t>
+  </si>
+  <si>
+    <t>Enter an email without '@' symbol (e.g., 'invalidemail.com') and click 'Register'.</t>
   </si>
 </sst>
 </file>
@@ -1134,11 +1146,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1511,11 +1524,10 @@
   <dimension ref="A1:F86"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="83.5703125" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
-    <col min="4" max="4" width="70.140625" customWidth="1"/>
-    <col min="5" max="5" width="73.85546875" customWidth="1"/>
+    <col min="2" max="2" width="86.28515625" customWidth="1"/>
+    <col min="3" max="3" width="78.7109375" customWidth="1"/>
+    <col min="4" max="4" width="121.42578125" customWidth="1"/>
+    <col min="5" max="5" width="135.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1546,16 +1558,16 @@
         <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1566,16 +1578,16 @@
         <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1586,16 +1598,16 @@
         <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E4" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1606,16 +1618,16 @@
         <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F5" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1626,16 +1638,16 @@
         <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F6" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1646,16 +1658,16 @@
         <v>96</v>
       </c>
       <c r="C7" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D7" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E7" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F7" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1666,16 +1678,16 @@
         <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D8" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F8" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1686,16 +1698,16 @@
         <v>98</v>
       </c>
       <c r="C9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D9" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1706,16 +1718,16 @@
         <v>99</v>
       </c>
       <c r="C10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E10" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F10" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1726,16 +1738,16 @@
         <v>100</v>
       </c>
       <c r="C11" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E11" t="s">
-        <v>350</v>
+        <v>274</v>
       </c>
       <c r="F11" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1746,16 +1758,16 @@
         <v>101</v>
       </c>
       <c r="C12" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E12" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F12" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1766,16 +1778,16 @@
         <v>102</v>
       </c>
       <c r="C13" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D13" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E13" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F13" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1783,19 +1795,19 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>103</v>
+        <v>350</v>
       </c>
       <c r="C14" t="s">
-        <v>343</v>
+        <v>173</v>
       </c>
       <c r="D14" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E14" t="s">
-        <v>344</v>
+        <v>277</v>
       </c>
       <c r="F14" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1803,19 +1815,19 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C15" t="s">
-        <v>343</v>
+        <v>173</v>
       </c>
       <c r="D15" t="s">
-        <v>348</v>
+        <v>194</v>
       </c>
       <c r="E15" t="s">
-        <v>347</v>
+        <v>278</v>
       </c>
       <c r="F15" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1823,19 +1835,19 @@
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s">
-        <v>343</v>
+        <v>173</v>
       </c>
       <c r="D16" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E16" t="s">
-        <v>345</v>
+        <v>279</v>
       </c>
       <c r="F16" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1843,19 +1855,19 @@
         <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D17" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E17" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="F17" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1863,19 +1875,19 @@
         <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C18" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D18" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E18" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="F18" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1883,19 +1895,19 @@
         <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D19" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E19" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F19" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1903,19 +1915,19 @@
         <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D20" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E20" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="F20" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1923,19 +1935,19 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C21" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D21" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E21" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="F21" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1943,19 +1955,19 @@
         <v>26</v>
       </c>
       <c r="B22" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C22" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D22" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E22" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="F22" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1963,19 +1975,19 @@
         <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C23" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D23" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E23" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="F23" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1983,19 +1995,19 @@
         <v>28</v>
       </c>
       <c r="B24" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C24" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D24" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E24" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="F24" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2003,19 +2015,19 @@
         <v>29</v>
       </c>
       <c r="B25" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C25" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D25" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E25" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="F25" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2023,19 +2035,19 @@
         <v>30</v>
       </c>
       <c r="B26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C26" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D26" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E26" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="F26" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2043,19 +2055,19 @@
         <v>31</v>
       </c>
       <c r="B27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C27" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D27" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E27" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="F27" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2063,19 +2075,19 @@
         <v>32</v>
       </c>
       <c r="B28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C28" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D28" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E28" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="F28" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2083,19 +2095,19 @@
         <v>33</v>
       </c>
       <c r="B29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C29" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D29" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E29" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="F29" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2103,19 +2115,19 @@
         <v>34</v>
       </c>
       <c r="B30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C30" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D30" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E30" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="F30" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2123,19 +2135,19 @@
         <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C31" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D31" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E31" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="F31" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2143,19 +2155,19 @@
         <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D32" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E32" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="F32" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2163,19 +2175,19 @@
         <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C33" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D33" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E33" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="F33" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2183,19 +2195,19 @@
         <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C34" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D34" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E34" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="F34" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2203,19 +2215,19 @@
         <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C35" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D35" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E35" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="F35" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2223,19 +2235,19 @@
         <v>40</v>
       </c>
       <c r="B36" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C36" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D36" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E36" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="F36" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2243,19 +2255,19 @@
         <v>41</v>
       </c>
       <c r="B37" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C37" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D37" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E37" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="F37" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2263,19 +2275,19 @@
         <v>42</v>
       </c>
       <c r="B38" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D38" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E38" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="F38" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2283,19 +2295,19 @@
         <v>43</v>
       </c>
       <c r="B39" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C39" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D39" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E39" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="F39" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2303,19 +2315,19 @@
         <v>44</v>
       </c>
       <c r="B40" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C40" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D40" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E40" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="F40" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2323,19 +2335,19 @@
         <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C41" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D41" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E41" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="F41" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2343,19 +2355,19 @@
         <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D42" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E42" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="F42" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2363,19 +2375,19 @@
         <v>47</v>
       </c>
       <c r="B43" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C43" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D43" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E43" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="F43" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2383,19 +2395,19 @@
         <v>48</v>
       </c>
       <c r="B44" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C44" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D44" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E44" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="F44" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2403,19 +2415,19 @@
         <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C45" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D45" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E45" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="F45" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2423,19 +2435,19 @@
         <v>50</v>
       </c>
       <c r="B46" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C46" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D46" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E46" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="F46" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2443,19 +2455,19 @@
         <v>51</v>
       </c>
       <c r="B47" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C47" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D47" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E47" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="F47" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2463,19 +2475,19 @@
         <v>52</v>
       </c>
       <c r="B48" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C48" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D48" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E48" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="F48" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2483,19 +2495,19 @@
         <v>53</v>
       </c>
       <c r="B49" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C49" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D49" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E49" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="F49" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2503,19 +2515,19 @@
         <v>54</v>
       </c>
       <c r="B50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C50" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D50" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E50" t="s">
-        <v>349</v>
+        <v>313</v>
       </c>
       <c r="F50" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2523,19 +2535,19 @@
         <v>55</v>
       </c>
       <c r="B51" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C51" t="s">
-        <v>177</v>
+        <v>346</v>
       </c>
       <c r="D51" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E51" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="F51" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2543,19 +2555,19 @@
         <v>56</v>
       </c>
       <c r="B52" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C52" t="s">
-        <v>177</v>
+        <v>346</v>
       </c>
       <c r="D52" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E52" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F52" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2563,19 +2575,19 @@
         <v>57</v>
       </c>
       <c r="B53" t="s">
-        <v>352</v>
+        <v>140</v>
       </c>
       <c r="C53" t="s">
-        <v>177</v>
+        <v>346</v>
       </c>
       <c r="D53" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E53" t="s">
-        <v>353</v>
+        <v>316</v>
       </c>
       <c r="F53" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2586,16 +2598,16 @@
         <v>141</v>
       </c>
       <c r="C54" t="s">
-        <v>177</v>
+        <v>346</v>
       </c>
       <c r="D54" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E54" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="F54" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2606,16 +2618,16 @@
         <v>142</v>
       </c>
       <c r="C55" t="s">
-        <v>177</v>
+        <v>346</v>
       </c>
       <c r="D55" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E55" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="F55" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2626,16 +2638,16 @@
         <v>143</v>
       </c>
       <c r="C56" t="s">
-        <v>177</v>
+        <v>346</v>
       </c>
       <c r="D56" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E56" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="F56" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2646,16 +2658,16 @@
         <v>144</v>
       </c>
       <c r="C57" t="s">
-        <v>177</v>
+        <v>346</v>
       </c>
       <c r="D57" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E57" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="F57" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2666,16 +2678,16 @@
         <v>145</v>
       </c>
       <c r="C58" t="s">
-        <v>177</v>
+        <v>346</v>
       </c>
       <c r="D58" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E58" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="F58" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2686,16 +2698,16 @@
         <v>146</v>
       </c>
       <c r="C59" t="s">
-        <v>177</v>
+        <v>346</v>
       </c>
       <c r="D59" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E59" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="F59" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2706,16 +2718,16 @@
         <v>147</v>
       </c>
       <c r="C60" t="s">
-        <v>177</v>
+        <v>346</v>
       </c>
       <c r="D60" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E60" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="F60" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2726,16 +2738,16 @@
         <v>148</v>
       </c>
       <c r="C61" t="s">
-        <v>177</v>
+        <v>346</v>
       </c>
       <c r="D61" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E61" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="F61" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2746,16 +2758,16 @@
         <v>149</v>
       </c>
       <c r="C62" t="s">
-        <v>177</v>
+        <v>346</v>
       </c>
       <c r="D62" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E62" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="F62" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2766,16 +2778,16 @@
         <v>150</v>
       </c>
       <c r="C63" t="s">
-        <v>177</v>
+        <v>346</v>
       </c>
       <c r="D63" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E63" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="F63" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2783,19 +2795,19 @@
         <v>68</v>
       </c>
       <c r="B64" t="s">
-        <v>151</v>
+        <v>348</v>
       </c>
       <c r="C64" t="s">
-        <v>177</v>
+        <v>346</v>
       </c>
       <c r="D64" t="s">
-        <v>240</v>
+        <v>349</v>
       </c>
       <c r="E64" t="s">
-        <v>319</v>
+        <v>347</v>
       </c>
       <c r="F64" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2803,19 +2815,19 @@
         <v>69</v>
       </c>
       <c r="B65" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C65" t="s">
-        <v>177</v>
+        <v>346</v>
       </c>
       <c r="D65" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E65" t="s">
-        <v>351</v>
+        <v>327</v>
       </c>
       <c r="F65" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2823,19 +2835,19 @@
         <v>70</v>
       </c>
       <c r="B66" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C66" t="s">
-        <v>177</v>
+        <v>346</v>
       </c>
       <c r="D66" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E66" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F66" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2843,19 +2855,19 @@
         <v>71</v>
       </c>
       <c r="B67" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C67" t="s">
-        <v>177</v>
+        <v>346</v>
       </c>
       <c r="D67" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E67" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="F67" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2863,19 +2875,19 @@
         <v>72</v>
       </c>
       <c r="B68" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C68" t="s">
-        <v>177</v>
+        <v>346</v>
       </c>
       <c r="D68" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E68" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="F68" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2883,19 +2895,19 @@
         <v>73</v>
       </c>
       <c r="B69" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C69" t="s">
-        <v>177</v>
+        <v>346</v>
       </c>
       <c r="D69" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E69" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="F69" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -2903,19 +2915,19 @@
         <v>74</v>
       </c>
       <c r="B70" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C70" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D70" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E70" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="F70" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2923,19 +2935,19 @@
         <v>75</v>
       </c>
       <c r="B71" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C71" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D71" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E71" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="F71" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2943,19 +2955,19 @@
         <v>76</v>
       </c>
       <c r="B72" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C72" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D72" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E72" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="F72" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2963,19 +2975,19 @@
         <v>77</v>
       </c>
       <c r="B73" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C73" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D73" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E73" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F73" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2983,19 +2995,19 @@
         <v>78</v>
       </c>
       <c r="B74" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C74" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D74" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E74" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="F74" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3003,19 +3015,19 @@
         <v>79</v>
       </c>
       <c r="B75" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C75" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D75" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E75" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="F75" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3023,19 +3035,19 @@
         <v>80</v>
       </c>
       <c r="B76" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C76" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D76" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E76" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="F76" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3043,19 +3055,19 @@
         <v>81</v>
       </c>
       <c r="B77" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C77" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D77" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E77" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="F77" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3063,19 +3075,19 @@
         <v>82</v>
       </c>
       <c r="B78" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C78" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D78" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E78" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="F78" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3083,19 +3095,19 @@
         <v>83</v>
       </c>
       <c r="B79" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C79" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D79" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E79" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="F79" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3103,19 +3115,19 @@
         <v>84</v>
       </c>
       <c r="B80" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C80" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D80" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E80" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="F80" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3123,19 +3135,19 @@
         <v>85</v>
       </c>
       <c r="B81" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C81" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D81" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E81" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="F81" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3143,19 +3155,19 @@
         <v>86</v>
       </c>
       <c r="B82" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C82" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D82" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E82" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="F82" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3163,79 +3175,79 @@
         <v>87</v>
       </c>
       <c r="B83" t="s">
+        <v>169</v>
+      </c>
+      <c r="C83" t="s">
+        <v>177</v>
+      </c>
+      <c r="D83" t="s">
+        <v>261</v>
+      </c>
+      <c r="E83" t="s">
+        <v>357</v>
+      </c>
+      <c r="F83" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B84" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C84" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D83" t="s">
-        <v>259</v>
-      </c>
-      <c r="E83" t="s">
-        <v>337</v>
-      </c>
-      <c r="F83" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>88</v>
-      </c>
-      <c r="B84" t="s">
+      <c r="D84" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B86" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C84" t="s">
-        <v>178</v>
-      </c>
-      <c r="D84" t="s">
-        <v>260</v>
-      </c>
-      <c r="E84" t="s">
-        <v>338</v>
-      </c>
-      <c r="F84" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>89</v>
-      </c>
-      <c r="B85" t="s">
-        <v>172</v>
-      </c>
-      <c r="C85" t="s">
-        <v>178</v>
-      </c>
-      <c r="D85" t="s">
-        <v>261</v>
-      </c>
-      <c r="E85" t="s">
-        <v>339</v>
-      </c>
-      <c r="F85" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>90</v>
-      </c>
-      <c r="B86" t="s">
-        <v>173</v>
-      </c>
-      <c r="C86" t="s">
-        <v>178</v>
-      </c>
-      <c r="D86" t="s">
-        <v>262</v>
-      </c>
-      <c r="E86" t="s">
-        <v>340</v>
-      </c>
-      <c r="F86" t="s">
-        <v>341</v>
+      <c r="C86" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>343</v>
       </c>
     </row>
   </sheetData>

--- a/85_Web_Application_Test_Cases/85_Web_Application_Test_Cases.xlsx
+++ b/85_Web_Application_Test_Cases/85_Web_Application_Test_Cases.xlsx
@@ -619,9 +619,6 @@
     <t>Inline quizzes and interactive workbooks are mentioned.</t>
   </si>
   <si>
-    <t>Clicking redirect user to the 'Register' page.</t>
-  </si>
-  <si>
     <t>Only beginner-level courses are displayed in the view.</t>
   </si>
   <si>
@@ -853,9 +850,6 @@
     <t>Click on the 'Download Theory Handbook' button.</t>
   </si>
   <si>
-    <t>Scroll to the bottom footer of the Theory page...</t>
-  </si>
-  <si>
     <t>Open the 'Courses' tab and check the main page title.</t>
   </si>
   <si>
@@ -1072,9 +1066,6 @@
     <t>Verify document download link for learning handbook</t>
   </si>
   <si>
-    <t>Connect to DB and execute: SELECT * FROM users WHERE email = 'test_user@mail.com'.</t>
-  </si>
-  <si>
     <t>Connect to DB and execute: SELECT password_hash FROM users WHERE email = 'test_user@mail.com'.</t>
   </si>
   <si>
@@ -1088,6 +1079,15 @@
   </si>
   <si>
     <t>Enter an email without '@' symbol (e.g., 'invalidemail.com') and click 'Register'.</t>
+  </si>
+  <si>
+    <t>Scroll to the bottom footer of the Theory page.</t>
+  </si>
+  <si>
+    <t>Clicking redirects the user to the 'Register' page.</t>
+  </si>
+  <si>
+    <t>Connect to DB and execute: SELECT u.first_name, u.last_name, u.email, r.role_name FROM users u JOIN user_roles r ON u.role_id = r.id WHERE u.email = 'test_user@mail.com'</t>
   </si>
 </sst>
 </file>
@@ -1527,7 +1527,7 @@
     <col min="2" max="2" width="86.28515625" customWidth="1"/>
     <col min="3" max="3" width="78.7109375" customWidth="1"/>
     <col min="4" max="4" width="121.42578125" customWidth="1"/>
-    <col min="5" max="5" width="135.42578125" customWidth="1"/>
+    <col min="5" max="5" width="165.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1564,10 +1564,10 @@
         <v>181</v>
       </c>
       <c r="E2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1584,10 +1584,10 @@
         <v>182</v>
       </c>
       <c r="E3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1604,10 +1604,10 @@
         <v>183</v>
       </c>
       <c r="E4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F4" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1624,10 +1624,10 @@
         <v>184</v>
       </c>
       <c r="E5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F5" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1644,10 +1644,10 @@
         <v>185</v>
       </c>
       <c r="E6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F6" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1664,10 +1664,10 @@
         <v>186</v>
       </c>
       <c r="E7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F7" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1684,10 +1684,10 @@
         <v>187</v>
       </c>
       <c r="E8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F8" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1704,10 +1704,10 @@
         <v>188</v>
       </c>
       <c r="E9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F9" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1724,10 +1724,10 @@
         <v>189</v>
       </c>
       <c r="E10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F10" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1744,10 +1744,10 @@
         <v>190</v>
       </c>
       <c r="E11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F11" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1764,10 +1764,10 @@
         <v>191</v>
       </c>
       <c r="E12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F12" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1784,10 +1784,10 @@
         <v>192</v>
       </c>
       <c r="E13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F13" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1795,7 +1795,7 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C14" t="s">
         <v>173</v>
@@ -1804,10 +1804,10 @@
         <v>193</v>
       </c>
       <c r="E14" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F14" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1815,7 +1815,7 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C15" t="s">
         <v>173</v>
@@ -1824,10 +1824,10 @@
         <v>194</v>
       </c>
       <c r="E15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F15" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1844,10 +1844,10 @@
         <v>195</v>
       </c>
       <c r="E16" t="s">
-        <v>279</v>
+        <v>355</v>
       </c>
       <c r="F16" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1864,10 +1864,10 @@
         <v>196</v>
       </c>
       <c r="E17" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F17" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1884,10 +1884,10 @@
         <v>197</v>
       </c>
       <c r="E18" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F18" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1904,10 +1904,10 @@
         <v>198</v>
       </c>
       <c r="E19" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F19" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1924,10 +1924,10 @@
         <v>199</v>
       </c>
       <c r="E20" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F20" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1944,10 +1944,10 @@
         <v>200</v>
       </c>
       <c r="E21" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F21" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1961,13 +1961,13 @@
         <v>174</v>
       </c>
       <c r="D22" t="s">
-        <v>201</v>
+        <v>356</v>
       </c>
       <c r="E22" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F22" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1981,13 +1981,13 @@
         <v>174</v>
       </c>
       <c r="D23" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E23" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F23" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2001,13 +2001,13 @@
         <v>174</v>
       </c>
       <c r="D24" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E24" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F24" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2021,13 +2021,13 @@
         <v>174</v>
       </c>
       <c r="D25" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E25" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F25" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2041,13 +2041,13 @@
         <v>174</v>
       </c>
       <c r="D26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E26" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2061,13 +2061,13 @@
         <v>174</v>
       </c>
       <c r="D27" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E27" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F27" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2081,13 +2081,13 @@
         <v>174</v>
       </c>
       <c r="D28" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E28" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F28" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2101,13 +2101,13 @@
         <v>174</v>
       </c>
       <c r="D29" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E29" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F29" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2121,13 +2121,13 @@
         <v>174</v>
       </c>
       <c r="D30" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E30" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F30" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2141,13 +2141,13 @@
         <v>174</v>
       </c>
       <c r="D31" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E31" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F31" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2161,13 +2161,13 @@
         <v>174</v>
       </c>
       <c r="D32" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E32" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F32" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2181,13 +2181,13 @@
         <v>174</v>
       </c>
       <c r="D33" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E33" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F33" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2201,13 +2201,13 @@
         <v>175</v>
       </c>
       <c r="D34" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E34" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F34" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2221,13 +2221,13 @@
         <v>175</v>
       </c>
       <c r="D35" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E35" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F35" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2241,13 +2241,13 @@
         <v>175</v>
       </c>
       <c r="D36" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E36" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F36" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2261,13 +2261,13 @@
         <v>175</v>
       </c>
       <c r="D37" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E37" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F37" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2281,13 +2281,13 @@
         <v>175</v>
       </c>
       <c r="D38" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E38" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F38" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2301,13 +2301,13 @@
         <v>175</v>
       </c>
       <c r="D39" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E39" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F39" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2321,13 +2321,13 @@
         <v>175</v>
       </c>
       <c r="D40" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E40" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F40" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2341,13 +2341,13 @@
         <v>175</v>
       </c>
       <c r="D41" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E41" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F41" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2361,13 +2361,13 @@
         <v>175</v>
       </c>
       <c r="D42" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E42" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F42" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2381,13 +2381,13 @@
         <v>175</v>
       </c>
       <c r="D43" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E43" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F43" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2401,13 +2401,13 @@
         <v>175</v>
       </c>
       <c r="D44" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E44" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F44" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2421,13 +2421,13 @@
         <v>175</v>
       </c>
       <c r="D45" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E45" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F45" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2441,13 +2441,13 @@
         <v>175</v>
       </c>
       <c r="D46" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E46" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F46" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2461,13 +2461,13 @@
         <v>175</v>
       </c>
       <c r="D47" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E47" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F47" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2481,13 +2481,13 @@
         <v>175</v>
       </c>
       <c r="D48" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E48" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F48" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2501,13 +2501,13 @@
         <v>175</v>
       </c>
       <c r="D49" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E49" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F49" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2521,13 +2521,13 @@
         <v>175</v>
       </c>
       <c r="D50" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E50" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F50" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2538,16 +2538,16 @@
         <v>138</v>
       </c>
       <c r="C51" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D51" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E51" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F51" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2558,16 +2558,16 @@
         <v>139</v>
       </c>
       <c r="C52" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D52" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E52" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F52" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2578,16 +2578,16 @@
         <v>140</v>
       </c>
       <c r="C53" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D53" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E53" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F53" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2598,16 +2598,16 @@
         <v>141</v>
       </c>
       <c r="C54" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D54" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E54" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F54" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2618,16 +2618,16 @@
         <v>142</v>
       </c>
       <c r="C55" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D55" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E55" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F55" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2638,16 +2638,16 @@
         <v>143</v>
       </c>
       <c r="C56" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D56" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E56" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F56" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2658,16 +2658,16 @@
         <v>144</v>
       </c>
       <c r="C57" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D57" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E57" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F57" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2678,16 +2678,16 @@
         <v>145</v>
       </c>
       <c r="C58" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D58" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E58" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F58" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2698,16 +2698,16 @@
         <v>146</v>
       </c>
       <c r="C59" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D59" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E59" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F59" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2718,16 +2718,16 @@
         <v>147</v>
       </c>
       <c r="C60" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D60" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E60" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F60" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2738,16 +2738,16 @@
         <v>148</v>
       </c>
       <c r="C61" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D61" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E61" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="F61" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2758,16 +2758,16 @@
         <v>149</v>
       </c>
       <c r="C62" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D62" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E62" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F62" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2778,16 +2778,16 @@
         <v>150</v>
       </c>
       <c r="C63" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D63" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E63" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F63" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2795,19 +2795,19 @@
         <v>68</v>
       </c>
       <c r="B64" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C64" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D64" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E64" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="F64" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2818,16 +2818,16 @@
         <v>151</v>
       </c>
       <c r="C65" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D65" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E65" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="F65" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2838,16 +2838,16 @@
         <v>152</v>
       </c>
       <c r="C66" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D66" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E66" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F66" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2858,16 +2858,16 @@
         <v>153</v>
       </c>
       <c r="C67" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D67" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E67" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F67" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2878,16 +2878,16 @@
         <v>154</v>
       </c>
       <c r="C68" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D68" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E68" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F68" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2898,16 +2898,16 @@
         <v>155</v>
       </c>
       <c r="C69" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D69" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E69" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F69" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -2921,13 +2921,13 @@
         <v>176</v>
       </c>
       <c r="D70" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E70" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F70" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2941,13 +2941,13 @@
         <v>176</v>
       </c>
       <c r="D71" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E71" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F71" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2961,13 +2961,13 @@
         <v>176</v>
       </c>
       <c r="D72" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E72" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F72" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2981,13 +2981,13 @@
         <v>176</v>
       </c>
       <c r="D73" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E73" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F73" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -3001,13 +3001,13 @@
         <v>176</v>
       </c>
       <c r="D74" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E74" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F74" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3021,13 +3021,13 @@
         <v>176</v>
       </c>
       <c r="D75" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E75" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F75" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3041,13 +3041,13 @@
         <v>176</v>
       </c>
       <c r="D76" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E76" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F76" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3061,13 +3061,13 @@
         <v>176</v>
       </c>
       <c r="D77" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E77" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F77" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3081,13 +3081,13 @@
         <v>176</v>
       </c>
       <c r="D78" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E78" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F78" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3101,13 +3101,13 @@
         <v>176</v>
       </c>
       <c r="D79" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E79" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F79" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3121,13 +3121,13 @@
         <v>176</v>
       </c>
       <c r="D80" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E80" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F80" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3141,13 +3141,13 @@
         <v>177</v>
       </c>
       <c r="D81" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E81" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F81" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3161,13 +3161,13 @@
         <v>177</v>
       </c>
       <c r="D82" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E82" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="F82" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3181,13 +3181,13 @@
         <v>177</v>
       </c>
       <c r="D83" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E83" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="F83" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="84" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3201,13 +3201,13 @@
         <v>178</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="85" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3215,19 +3215,19 @@
         <v>89</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>179</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="86" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3241,13 +3241,13 @@
         <v>180</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
   </sheetData>
